--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0010_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0010_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -11409,7 +11408,7 @@
         <v>4.8043151028600057</v>
       </c>
       <c r="C32" s="0">
-        <v>1.2903225806451602</v>
+        <v>1.2903225806451601</v>
       </c>
       <c r="D32" s="0">
         <v>4.7782968609130361</v>
@@ -12678,7 +12677,7 @@
         <v>0</v>
       </c>
       <c r="BL35" s="0">
-        <v>0.63049293083683911</v>
+        <v>0.6304929308368391</v>
       </c>
       <c r="BM35" s="0">
         <v>0</v>
@@ -13243,7 +13242,7 @@
         <v>0.88240936121235292</v>
       </c>
       <c r="K37" s="0">
-        <v>0.91220068415051237</v>
+        <v>0.91220068415051236</v>
       </c>
       <c r="L37" s="0">
         <v>4.2088438998401667</v>
@@ -13255,7 +13254,7 @@
         <v>15.264797507788147</v>
       </c>
       <c r="O37" s="0">
-        <v>0.55368795728692855</v>
+        <v>0.55368795728692854</v>
       </c>
       <c r="P37" s="0">
         <v>9.1110731957003832</v>
@@ -13758,7 +13757,7 @@
         <v>0</v>
       </c>
       <c r="BJ38" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK38" s="0">
         <v>0</v>
@@ -13940,7 +13939,7 @@
         <v>13.669846636879592</v>
       </c>
       <c r="B39" s="0">
-        <v>0.17561465127947804</v>
+        <v>0.17561465127947803</v>
       </c>
       <c r="C39" s="0">
         <v>0.76889085285019809</v>
@@ -14243,7 +14242,7 @@
         <v>0</v>
       </c>
       <c r="CY39" s="0">
-        <v>1.6046681254558704</v>
+        <v>1.6046681254558703</v>
       </c>
       <c r="CZ39" s="0">
         <v>0</v>
@@ -14458,7 +14457,7 @@
         <v>0</v>
       </c>
       <c r="BB40" s="0">
-        <v>0.62093435836782907</v>
+        <v>0.62093435836782906</v>
       </c>
       <c r="BC40" s="0">
         <v>0.20314880650076161</v>
@@ -14700,7 +14699,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="0">
-        <v>0.65420560747663859</v>
+        <v>0.65420560747663858</v>
       </c>
       <c r="O41" s="0">
         <v>15.740557642871341</v>
@@ -15077,7 +15076,7 @@
         <v>0.13774104683195582</v>
       </c>
       <c r="S42" s="0">
-        <v>17.135692393424336</v>
+        <v>17.135692393424335</v>
       </c>
       <c r="T42" s="0">
         <v>0</v>
@@ -15179,7 +15178,7 @@
         <v>4.7424972211930303</v>
       </c>
       <c r="BA42" s="0">
-        <v>1.4155394778232136</v>
+        <v>1.4155394778232135</v>
       </c>
       <c r="BB42" s="0">
         <v>5.7066824364281441</v>
@@ -15224,7 +15223,7 @@
         <v>0.54035798716649741</v>
       </c>
       <c r="BP42" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ42" s="0">
         <v>0.035893754486719283</v>
@@ -15649,7 +15648,7 @@
         <v>0.94876660341555885</v>
       </c>
       <c r="CK43" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL43" s="0">
         <v>0.10420613868889721</v>
@@ -15709,7 +15708,7 @@
         <v>0.72859744990892472</v>
       </c>
       <c r="DE43" s="0">
-        <v>12.759787336877706</v>
+        <v>12.759787336877705</v>
       </c>
       <c r="DF43" s="0">
         <v>10.173824130879337</v>
@@ -15807,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="U44" s="0">
-        <v>0.94813162297824794</v>
+        <v>0.94813162297824793</v>
       </c>
       <c r="V44" s="0">
         <v>12.729779411764694</v>
@@ -15855,7 +15854,7 @@
         <v>13.003095975232187</v>
       </c>
       <c r="AK44" s="0">
-        <v>1.7606418542455971</v>
+        <v>1.760641854245597</v>
       </c>
       <c r="AL44" s="0">
         <v>0</v>
@@ -16074,7 +16073,7 @@
         <v>11.841469308844843</v>
       </c>
       <c r="DF44" s="0">
-        <v>5.5725971370143102</v>
+        <v>5.5725971370143101</v>
       </c>
       <c r="DG44" s="0">
         <v>0.91463414634146256</v>
@@ -16199,7 +16198,7 @@
         <v>0.78515346181298995</v>
       </c>
       <c r="AE45" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF45" s="0">
         <v>0</v>
@@ -16385,7 +16384,7 @@
         <v>6.4249820531227506</v>
       </c>
       <c r="CO45" s="0">
-        <v>0.066120074054482878</v>
+        <v>0.066120074054482877</v>
       </c>
       <c r="CP45" s="0">
         <v>0.059959227725146849</v>
@@ -16415,7 +16414,7 @@
         <v>0.3355704697986574</v>
       </c>
       <c r="CY45" s="0">
-        <v>2.7716994894237757</v>
+        <v>2.7716994894237756</v>
       </c>
       <c r="CZ45" s="0">
         <v>2.4003728734560688</v>
@@ -16427,7 +16426,7 @@
         <v>0</v>
       </c>
       <c r="DC45" s="0">
-        <v>0.20206555904804655</v>
+        <v>0.20206555904804654</v>
       </c>
       <c r="DD45" s="0">
         <v>7.9599271402550018</v>
@@ -16436,7 +16435,7 @@
         <v>6.6698888351860743</v>
       </c>
       <c r="DF45" s="0">
-        <v>2.1472392638036793</v>
+        <v>2.1472392638036792</v>
       </c>
       <c r="DG45" s="0">
         <v>5.4878048780487756</v>
@@ -16750,7 +16749,7 @@
         <v>0.48928854800317334</v>
       </c>
       <c r="CP46" s="0">
-        <v>0.26382060199064617</v>
+        <v>0.26382060199064616</v>
       </c>
       <c r="CQ46" s="0">
         <v>5.8680104031209313</v>
@@ -16983,7 +16982,7 @@
         <v>3.3424491036159378</v>
       </c>
       <c r="AY47" s="0">
-        <v>3.3569261880687718</v>
+        <v>3.3569261880687717</v>
       </c>
       <c r="AZ47" s="0">
         <v>2.7232308262319505</v>
@@ -17028,7 +17027,7 @@
         <v>9.5602294455067369</v>
       </c>
       <c r="BN47" s="0">
-        <v>1.1176653213287851</v>
+        <v>1.117665321328785</v>
       </c>
       <c r="BO47" s="0">
         <v>10.233029381965601</v>
@@ -17091,7 +17090,7 @@
         <v>14.89333510003982</v>
       </c>
       <c r="CI47" s="0">
-        <v>10.782029950083246</v>
+        <v>10.782029950083245</v>
       </c>
       <c r="CJ47" s="0">
         <v>15.43327008222651</v>
@@ -17136,7 +17135,7 @@
         <v>0.98289042591918918</v>
       </c>
       <c r="CX47" s="0">
-        <v>4.9856184084372242</v>
+        <v>4.9856184084372241</v>
       </c>
       <c r="CY47" s="0">
         <v>0</v>
@@ -17537,7 +17536,7 @@
         <v>2.4390243902439002</v>
       </c>
       <c r="DK48" s="0">
-        <v>1.3869625520110947</v>
+        <v>1.3869625520110946</v>
       </c>
       <c r="DL48" s="0">
         <v>11.096605744125316</v>
@@ -17653,7 +17652,7 @@
         <v>3.5789473684210491</v>
       </c>
       <c r="AG49" s="0">
-        <v>16.36487098234494</v>
+        <v>16.364870982344939</v>
       </c>
       <c r="AH49" s="0">
         <v>13.011417697431007</v>
@@ -17710,7 +17709,7 @@
         <v>0.080889787664307308</v>
       </c>
       <c r="AZ49" s="0">
-        <v>0.20377917747313804</v>
+        <v>0.20377917747313803</v>
       </c>
       <c r="BA49" s="0">
         <v>0.53475935828876953</v>
@@ -17740,7 +17739,7 @@
         <v>16.449704142011818</v>
       </c>
       <c r="BJ49" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK49" s="0">
         <v>0.041211621677312966</v>
@@ -17878,7 +17877,7 @@
         <v>14.683430624158049</v>
       </c>
       <c r="DD49" s="0">
-        <v>5.1912568306010885</v>
+        <v>5.1912568306010884</v>
       </c>
       <c r="DE49" s="0">
         <v>0</v>
@@ -18383,7 +18382,7 @@
         <v>6.7316841103710692</v>
       </c>
       <c r="AI51" s="0">
-        <v>5.381574946792334</v>
+        <v>5.3815749467923339</v>
       </c>
       <c r="AJ51" s="0">
         <v>0</v>
@@ -18461,7 +18460,7 @@
         <v>1.0207496653279777</v>
       </c>
       <c r="BI51" s="0">
-        <v>8.1118881118881046</v>
+        <v>8.1118881118881045</v>
       </c>
       <c r="BJ51" s="0">
         <v>0</v>
@@ -18506,7 +18505,7 @@
         <v>0.13157894736842093</v>
       </c>
       <c r="BX51" s="0">
-        <v>0.33655868742111878</v>
+        <v>0.33655868742111877</v>
       </c>
       <c r="BY51" s="0">
         <v>0</v>
@@ -18563,7 +18562,7 @@
         <v>14.785945557021213</v>
       </c>
       <c r="CQ51" s="0">
-        <v>1.8855656697009085</v>
+        <v>1.8855656697009084</v>
       </c>
       <c r="CR51" s="0">
         <v>0.047938638542665342</v>
@@ -18877,7 +18876,7 @@
         <v>0</v>
       </c>
       <c r="CA52" s="0">
-        <v>2.105263157894735</v>
+        <v>2.1052631578947349</v>
       </c>
       <c r="CB52" s="0">
         <v>2.3622047244094468</v>
@@ -18904,7 +18903,7 @@
         <v>0.66555740432612254</v>
       </c>
       <c r="CJ52" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK52" s="0">
         <v>2.7586206896551699</v>
@@ -18919,7 +18918,7 @@
         <v>0.035893754486719283</v>
       </c>
       <c r="CO52" s="0">
-        <v>5.9111346204707696</v>
+        <v>5.9111346204707695</v>
       </c>
       <c r="CP52" s="0">
         <v>9.8093296558340235</v>
@@ -19185,7 +19184,7 @@
         <v>0.016733601070950455</v>
       </c>
       <c r="BI53" s="0">
-        <v>0.64550833781602957</v>
+        <v>0.64550833781602956</v>
       </c>
       <c r="BJ53" s="0">
         <v>0</v>
@@ -19532,7 +19531,7 @@
         <v>0</v>
       </c>
       <c r="BD54" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE54" s="0">
         <v>0</v>
@@ -19822,7 +19821,7 @@
         <v>0</v>
       </c>
       <c r="AF55" s="0">
-        <v>2.105263157894735</v>
+        <v>2.1052631578947349</v>
       </c>
       <c r="AG55" s="0">
         <v>0</v>
@@ -20307,7 +20306,7 @@
         <v>0</v>
       </c>
       <c r="BU56" s="0">
-        <v>0.52844264843021394</v>
+        <v>0.52844264843021393</v>
       </c>
       <c r="BV56" s="0">
         <v>0</v>
@@ -20355,7 +20354,7 @@
         <v>0</v>
       </c>
       <c r="CK56" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL56" s="0">
         <v>0</v>
@@ -20442,7 +20441,7 @@
         <v>2.3504273504273483</v>
       </c>
       <c r="DN56" s="0">
-        <v>0.58593749999999945</v>
+        <v>0.58593749999999944</v>
       </c>
       <c r="DO56" s="0">
         <v>0</v>
@@ -24636,7 +24635,7 @@
         <v>0</v>
       </c>
       <c r="BP68" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ68" s="0">
         <v>0</v>
@@ -25450,7 +25449,7 @@
         <v>0</v>
       </c>
       <c r="CT70" s="0">
-        <v>0.22026431718061657</v>
+        <v>0.22026431718061656</v>
       </c>
       <c r="CU70" s="0">
         <v>0</v>
@@ -25581,7 +25580,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="0">
-        <v>0.94813162297824794</v>
+        <v>0.94813162297824793</v>
       </c>
       <c r="V71" s="0">
         <v>0</v>
@@ -25689,7 +25688,7 @@
         <v>3.0832476875642318</v>
       </c>
       <c r="BE71" s="0">
-        <v>1.6408813877168294</v>
+        <v>1.6408813877168293</v>
       </c>
       <c r="BF71" s="0">
         <v>0</v>
@@ -25812,7 +25811,7 @@
         <v>0.022114108801415285</v>
       </c>
       <c r="CT71" s="0">
-        <v>0.70084100921105264</v>
+        <v>0.70084100921105263</v>
       </c>
       <c r="CU71" s="0">
         <v>0</v>
@@ -25943,7 +25942,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="0">
-        <v>4.8522030117122093</v>
+        <v>4.8522030117122092</v>
       </c>
       <c r="V72" s="0">
         <v>0</v>
@@ -25982,7 +25981,7 @@
         <v>0</v>
       </c>
       <c r="AH72" s="0">
-        <v>12.535680304471923</v>
+        <v>12.535680304471922</v>
       </c>
       <c r="AI72" s="0">
         <v>0</v>
@@ -26700,7 +26699,7 @@
         <v>0</v>
       </c>
       <c r="AF74" s="0">
-        <v>2.7368421052631558</v>
+        <v>2.7368421052631557</v>
       </c>
       <c r="AG74" s="0">
         <v>0</v>
@@ -26844,10 +26843,10 @@
         <v>9.3233082706766837</v>
       </c>
       <c r="CB74" s="0">
-        <v>6.1417322834645614</v>
+        <v>6.1417322834645613</v>
       </c>
       <c r="CC74" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD74" s="0">
         <v>0.076923076923076858</v>
@@ -27053,7 +27052,7 @@
         <v>8.215818516247694</v>
       </c>
       <c r="AC75" s="0">
-        <v>9.7163120567375803</v>
+        <v>9.7163120567375802</v>
       </c>
       <c r="AD75" s="0">
         <v>6.2098501070663756</v>
@@ -27068,7 +27067,7 @@
         <v>0</v>
       </c>
       <c r="AH75" s="0">
-        <v>1.5461465271170301</v>
+        <v>1.54614652711703</v>
       </c>
       <c r="AI75" s="0">
         <v>0.30404378230465157</v>
@@ -27104,7 +27103,7 @@
         <v>0</v>
       </c>
       <c r="AT75" s="0">
-        <v>9.6828046744574206</v>
+        <v>9.6828046744574205</v>
       </c>
       <c r="AU75" s="0">
         <v>0.29673590504451014</v>
@@ -27155,7 +27154,7 @@
         <v>0.27639579878385823</v>
       </c>
       <c r="BK75" s="0">
-        <v>3.4617762208942891</v>
+        <v>3.461776220894289</v>
       </c>
       <c r="BL75" s="0">
         <v>0</v>
@@ -27227,7 +27226,7 @@
         <v>0.079501788790247718</v>
       </c>
       <c r="CI75" s="0">
-        <v>0.43261231281197971</v>
+        <v>0.4326123128119797</v>
       </c>
       <c r="CJ75" s="0">
         <v>0</v>
@@ -27529,7 +27528,7 @@
         <v>0.093138776777398249</v>
       </c>
       <c r="BO76" s="0">
-        <v>6.4842958459979681</v>
+        <v>6.484295845997968</v>
       </c>
       <c r="BP76" s="0">
         <v>2.9320987654320958</v>
@@ -27538,7 +27537,7 @@
         <v>11.091170136396256</v>
       </c>
       <c r="BR76" s="0">
-        <v>7.7742794865584815</v>
+        <v>7.7742794865584814</v>
       </c>
       <c r="BS76" s="0">
         <v>0</v>
@@ -27562,7 +27561,7 @@
         <v>0</v>
       </c>
       <c r="BZ76" s="0">
-        <v>2.6461295418641369</v>
+        <v>2.6461295418641368</v>
       </c>
       <c r="CA76" s="0">
         <v>7.6691729323308202</v>
@@ -27580,7 +27579,7 @@
         <v>5.5238095238095193</v>
       </c>
       <c r="CF76" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG76" s="0">
         <v>0.56727530579684404</v>
@@ -27649,7 +27648,7 @@
         <v>4.388714733542316</v>
       </c>
       <c r="DC76" s="0">
-        <v>4.8944768747193495</v>
+        <v>4.8944768747193494</v>
       </c>
       <c r="DD76" s="0">
         <v>3.9344262295081935</v>
@@ -27849,7 +27848,7 @@
         <v>9.5590959614672002</v>
       </c>
       <c r="BA77" s="0">
-        <v>9.5942120163573375</v>
+        <v>9.5942120163573374</v>
       </c>
       <c r="BB77" s="0">
         <v>13.128326434062673</v>
@@ -27858,7 +27857,7 @@
         <v>12.27780599288978</v>
       </c>
       <c r="BD77" s="0">
-        <v>1.130524152106885</v>
+        <v>1.1305241521068849</v>
       </c>
       <c r="BE77" s="0">
         <v>1.5002344116268154</v>
@@ -27930,7 +27929,7 @@
         <v>2.7067669172932307</v>
       </c>
       <c r="CB77" s="0">
-        <v>6.9291338582677105</v>
+        <v>6.9291338582677104</v>
       </c>
       <c r="CC77" s="0">
         <v>3.037120359955003</v>
@@ -27942,7 +27941,7 @@
         <v>5.5238095238095193</v>
       </c>
       <c r="CF77" s="0">
-        <v>2.2452504317789273</v>
+        <v>2.2452504317789272</v>
       </c>
       <c r="CG77" s="0">
         <v>2.3754653430242847</v>
@@ -27972,7 +27971,7 @@
         <v>0</v>
       </c>
       <c r="CP77" s="0">
-        <v>9.3776232162129674</v>
+        <v>9.3776232162129673</v>
       </c>
       <c r="CQ77" s="0">
         <v>1.5767230169050701</v>
@@ -28148,7 +28147,7 @@
         <v>0.6147540983606552</v>
       </c>
       <c r="AF78" s="0">
-        <v>4.8421052631578903</v>
+        <v>4.8421052631578902</v>
       </c>
       <c r="AG78" s="0">
         <v>1.5165233137166125</v>
@@ -28184,7 +28183,7 @@
         <v>6.1373390557939862</v>
       </c>
       <c r="AR78" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS78" s="0">
         <v>0</v>
@@ -28298,7 +28297,7 @@
         <v>6.6741657292838328</v>
       </c>
       <c r="CD78" s="0">
-        <v>7.4230769230769163</v>
+        <v>7.4230769230769162</v>
       </c>
       <c r="CE78" s="0">
         <v>1.5238095238095224</v>
@@ -28582,7 +28581,7 @@
         <v>5.6881665820213252</v>
       </c>
       <c r="BD79" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE79" s="0">
         <v>0</v>
@@ -28699,7 +28698,7 @@
         <v>5.9959227725146844</v>
       </c>
       <c r="CQ79" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR79" s="0">
         <v>1.3263023330137413</v>
@@ -28854,7 +28853,7 @@
         <v>8.333333333333325</v>
       </c>
       <c r="Z80" s="0">
-        <v>3.2944406314344517</v>
+        <v>3.2944406314344516</v>
       </c>
       <c r="AA80" s="0">
         <v>0.087950747581354363</v>
@@ -28998,10 +28997,10 @@
         <v>2.4246192104445115</v>
       </c>
       <c r="BV80" s="0">
-        <v>6.4373464373464318</v>
+        <v>6.4373464373464317</v>
       </c>
       <c r="BW80" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX80" s="0">
         <v>0.46276819520403834</v>
@@ -29384,7 +29383,7 @@
         <v>6.974128233970748</v>
       </c>
       <c r="CD81" s="0">
-        <v>5.3076923076923031</v>
+        <v>5.307692307692303</v>
       </c>
       <c r="CE81" s="0">
         <v>0</v>
@@ -29393,7 +29392,7 @@
         <v>5.3540587219343649</v>
       </c>
       <c r="CG81" s="0">
-        <v>8.6864031200141732</v>
+        <v>8.6864031200141731</v>
       </c>
       <c r="CH81" s="0">
         <v>6.9166556247515505</v>
@@ -29420,7 +29419,7 @@
         <v>0</v>
       </c>
       <c r="CP81" s="0">
-        <v>0.82743734260702651</v>
+        <v>0.8274373426070265</v>
       </c>
       <c r="CQ81" s="0">
         <v>0</v>
@@ -29746,7 +29745,7 @@
         <v>3.0371203599550367</v>
       </c>
       <c r="CD82" s="0">
-        <v>2.153846153846176</v>
+        <v>2.1538461538461759</v>
       </c>
       <c r="CE82" s="0">
         <v>0</v>
@@ -29764,7 +29763,7 @@
         <v>1.1647254575707273</v>
       </c>
       <c r="CJ82" s="0">
-        <v>8.1593927893738965</v>
+        <v>8.1593927893738964</v>
       </c>
       <c r="CK82" s="0">
         <v>0</v>
@@ -29931,7 +29930,7 @@
         <v>1.4246323529411751</v>
       </c>
       <c r="W83" s="0">
-        <v>0.20512820512820496</v>
+        <v>0.20512820512820495</v>
       </c>
       <c r="X83" s="0">
         <v>12.279704377487198</v>
@@ -30123,7 +30122,7 @@
         <v>1.1130250430634678</v>
       </c>
       <c r="CI83" s="0">
-        <v>0.26622296173044902</v>
+        <v>0.26622296173044901</v>
       </c>
       <c r="CJ83" s="0">
         <v>4.1429475015812738</v>
@@ -30132,7 +30131,7 @@
         <v>0</v>
       </c>
       <c r="CL83" s="0">
-        <v>0.047366426676771462</v>
+        <v>0.047366426676771461</v>
       </c>
       <c r="CM83" s="0">
         <v>0</v>
@@ -30186,7 +30185,7 @@
         <v>0.044903457566232555</v>
       </c>
       <c r="DD83" s="0">
-        <v>0.12750455373406181</v>
+        <v>0.1275045537340618</v>
       </c>
       <c r="DE83" s="0">
         <v>0</v>
@@ -30467,7 +30466,7 @@
         <v>0</v>
       </c>
       <c r="CC84" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD84" s="0">
         <v>0</v>
@@ -30769,7 +30768,7 @@
         <v>0.53547523427041455</v>
       </c>
       <c r="BI85" s="0">
-        <v>0.032275416890801476</v>
+        <v>0.032275416890801475</v>
       </c>
       <c r="BJ85" s="0">
         <v>0.011055831951354331</v>
@@ -30814,7 +30813,7 @@
         <v>10.394736842105255</v>
       </c>
       <c r="BX85" s="0">
-        <v>6.0580563735801381</v>
+        <v>6.058056373580138</v>
       </c>
       <c r="BY85" s="0">
         <v>4.4732441471571862</v>
@@ -30895,7 +30894,7 @@
         <v>0.23969319271332676</v>
       </c>
       <c r="CY85" s="0">
-        <v>0.77802090931193702</v>
+        <v>0.77802090931193701</v>
       </c>
       <c r="CZ85" s="0">
         <v>0</v>
@@ -30981,13 +30980,13 @@
         <v>0</v>
       </c>
       <c r="K86" s="0">
-        <v>6.7274800456100286</v>
+        <v>6.7274800456100285</v>
       </c>
       <c r="L86" s="0">
         <v>0.05327650506126793</v>
       </c>
       <c r="M86" s="0">
-        <v>1.4553014553014541</v>
+        <v>1.455301455301454</v>
       </c>
       <c r="N86" s="0">
         <v>0</v>
@@ -31305,7 +31304,7 @@
         <v>0</v>
       </c>
       <c r="DO86" s="0">
-        <v>2.9126213592232984</v>
+        <v>2.9126213592232983</v>
       </c>
       <c r="DP86" s="0">
         <v>0</v>
@@ -31699,7 +31698,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="0">
-        <v>0.66445182724252439</v>
+        <v>0.66445182724252438</v>
       </c>
       <c r="J88" s="0">
         <v>0</v>
@@ -32040,7 +32039,7 @@
         <v>0.22944088878154792</v>
       </c>
       <c r="B89" s="0">
-        <v>11.54039136979427</v>
+        <v>11.540391369794269</v>
       </c>
       <c r="C89" s="0">
         <v>10.861688024745902</v>
@@ -32166,7 +32165,7 @@
         <v>0</v>
       </c>
       <c r="AR89" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS89" s="0">
         <v>0</v>
@@ -32399,7 +32398,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>1.3041903151793251</v>
+        <v>1.304190315179325</v>
       </c>
       <c r="B90" s="0">
         <v>11.929252383341685</v>
@@ -32770,7 +32769,7 @@
         <v>3.0844012372956224</v>
       </c>
       <c r="D91" s="0">
-        <v>1.1802311285960157</v>
+        <v>1.1802311285960156</v>
       </c>
       <c r="E91" s="0">
         <v>3.1398934679001935</v>
@@ -33159,7 +33158,7 @@
         <v>7.7783697389451181</v>
       </c>
       <c r="M92" s="0">
-        <v>2.0790020790020774</v>
+        <v>2.0790020790020773</v>
       </c>
       <c r="N92" s="0">
         <v>11.059190031152639</v>
@@ -33506,7 +33505,7 @@
         <v>0.60096153846153799</v>
       </c>
       <c r="H93" s="0">
-        <v>8.9009990917347786</v>
+        <v>8.9009990917347785</v>
       </c>
       <c r="I93" s="0">
         <v>8.3554817275747446</v>
@@ -34263,7 +34262,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="0">
-        <v>6.8264140429088816</v>
+        <v>6.8264140429088815</v>
       </c>
       <c r="T95" s="0">
         <v>0.40975209997951201</v>
@@ -34960,7 +34959,7 @@
         <v>0.066445182724252441</v>
       </c>
       <c r="J97" s="0">
-        <v>5.908306157682711</v>
+        <v>5.9083061576827109</v>
       </c>
       <c r="K97" s="0">
         <v>0</v>
@@ -36067,7 +36066,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="0">
-        <v>22.993827160493805</v>
+        <v>22.993827160493804</v>
       </c>
       <c r="R100" s="0">
         <v>24.931129476583997</v>
